--- a/data/nzd0081/nzd0081.xlsx
+++ b/data/nzd0081/nzd0081.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E344"/>
+  <dimension ref="A1:E345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7656,6 +7656,27 @@
         <v>325.81</v>
       </c>
       <c r="E344" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>338.55</v>
+      </c>
+      <c r="C345" t="n">
+        <v>314.98</v>
+      </c>
+      <c r="D345" t="n">
+        <v>325.73</v>
+      </c>
+      <c r="E345" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -7672,7 +7693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11245,6 +11266,16 @@
       </c>
       <c r="B357" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -11413,28 +11444,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1902020733562883</v>
+        <v>0.1870474401789561</v>
       </c>
       <c r="J2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08629317188394425</v>
+        <v>0.08389024167437464</v>
       </c>
       <c r="M2" t="n">
-        <v>3.784078003369633</v>
+        <v>3.78838843723978</v>
       </c>
       <c r="N2" t="n">
-        <v>21.01366100621483</v>
+        <v>21.03592601708334</v>
       </c>
       <c r="O2" t="n">
-        <v>4.584065990604283</v>
+        <v>4.58649386973136</v>
       </c>
       <c r="P2" t="n">
-        <v>338.8226320232845</v>
+        <v>338.8566692024423</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11491,28 +11522,28 @@
         <v>0.1106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1764855480376395</v>
+        <v>0.1725082595626963</v>
       </c>
       <c r="J3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06752630031852913</v>
+        <v>0.06476847286836118</v>
       </c>
       <c r="M3" t="n">
-        <v>3.928253604409327</v>
+        <v>3.937946236894629</v>
       </c>
       <c r="N3" t="n">
-        <v>23.5951488744424</v>
+        <v>23.65904996913152</v>
       </c>
       <c r="O3" t="n">
-        <v>4.857483800739062</v>
+        <v>4.864056945506654</v>
       </c>
       <c r="P3" t="n">
-        <v>317.0219646813484</v>
+        <v>317.0648779688128</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11569,28 +11600,28 @@
         <v>0.0882</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06460214021342313</v>
+        <v>0.06559099032332476</v>
       </c>
       <c r="J4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01057300798585425</v>
+        <v>0.01096229087159373</v>
       </c>
       <c r="M4" t="n">
-        <v>3.786668520069285</v>
+        <v>3.780037675323008</v>
       </c>
       <c r="N4" t="n">
-        <v>21.42494897969331</v>
+        <v>21.37085698786291</v>
       </c>
       <c r="O4" t="n">
-        <v>4.628709213127706</v>
+        <v>4.622862423635697</v>
       </c>
       <c r="P4" t="n">
-        <v>322.3128055798014</v>
+        <v>322.3021362986334</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11628,7 +11659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E344"/>
+  <dimension ref="A1:E345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20919,6 +20950,33 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-35.462960253806955,174.43595851812873</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-35.46345137108843,174.4366770256903</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-35.46365845936953,174.43754548501335</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0081/nzd0081.xlsx
+++ b/data/nzd0081/nzd0081.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E345"/>
+  <dimension ref="A1:E348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7679,6 +7679,69 @@
       <c r="E345" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>337.2</v>
+      </c>
+      <c r="C346" t="n">
+        <v>315.04</v>
+      </c>
+      <c r="D346" t="n">
+        <v>322.52</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>338.83</v>
+      </c>
+      <c r="C347" t="n">
+        <v>316.51</v>
+      </c>
+      <c r="D347" t="n">
+        <v>323.72</v>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>339.82</v>
+      </c>
+      <c r="C348" t="n">
+        <v>316.51</v>
+      </c>
+      <c r="D348" t="n">
+        <v>323.72</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11276,6 +11339,36 @@
       </c>
       <c r="B358" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11444,28 +11537,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1870474401789561</v>
+        <v>0.1779499784557935</v>
       </c>
       <c r="J2" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08389024167437464</v>
+        <v>0.07709307483307482</v>
       </c>
       <c r="M2" t="n">
-        <v>3.78838843723978</v>
+        <v>3.799949499974066</v>
       </c>
       <c r="N2" t="n">
-        <v>21.03592601708334</v>
+        <v>21.09844333439019</v>
       </c>
       <c r="O2" t="n">
-        <v>4.58649386973136</v>
+        <v>4.593304184831458</v>
       </c>
       <c r="P2" t="n">
-        <v>338.8566692024423</v>
+        <v>338.9551651515908</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11522,28 +11615,28 @@
         <v>0.1106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1725082595626963</v>
+        <v>0.1626953886694804</v>
       </c>
       <c r="J3" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06476847286836118</v>
+        <v>0.05845043507815473</v>
       </c>
       <c r="M3" t="n">
-        <v>3.937946236894629</v>
+        <v>3.956777543747812</v>
       </c>
       <c r="N3" t="n">
-        <v>23.65904996913152</v>
+        <v>23.73110295706368</v>
       </c>
       <c r="O3" t="n">
-        <v>4.864056945506654</v>
+        <v>4.871457990895917</v>
       </c>
       <c r="P3" t="n">
-        <v>317.0648779688128</v>
+        <v>317.1711272621526</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11600,28 +11693,28 @@
         <v>0.0882</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06559099032332476</v>
+        <v>0.0643051880535237</v>
       </c>
       <c r="J4" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K4" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01096229087159373</v>
+        <v>0.01074261646082697</v>
       </c>
       <c r="M4" t="n">
-        <v>3.780037675323008</v>
+        <v>3.754309768150532</v>
       </c>
       <c r="N4" t="n">
-        <v>21.37085698786291</v>
+        <v>21.19352772072725</v>
       </c>
       <c r="O4" t="n">
-        <v>4.622862423635697</v>
+        <v>4.603642875020525</v>
       </c>
       <c r="P4" t="n">
-        <v>322.3021362986334</v>
+        <v>322.3160526691666</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11659,7 +11752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E345"/>
+  <dimension ref="A1:E348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20977,6 +21070,87 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-35.46297142622156,174.43595261965774</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-35.46345087453584,174.43667728784334</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-35.463685024992785,174.4375314599817</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-35.46295793656536,174.4359597415151</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-35.46343870899718,174.4366837105916</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-35.46367509391885,174.43753670298526</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:05+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-35.46294974346111,174.43596406705925</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-35.46343870899718,174.4366837105916</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-35.46367509391885,174.43753670298526</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0081/nzd0081.xlsx
+++ b/data/nzd0081/nzd0081.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E348"/>
+  <dimension ref="A1:E349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7740,6 +7740,27 @@
         <v>323.72</v>
       </c>
       <c r="E348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>341.04</v>
+      </c>
+      <c r="C349" t="n">
+        <v>317.14</v>
+      </c>
+      <c r="D349" t="n">
+        <v>322.88</v>
+      </c>
+      <c r="E349" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -7756,7 +7777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B361"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11369,6 +11390,16 @@
       </c>
       <c r="B361" t="n">
         <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -11537,28 +11568,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1779499784557935</v>
+        <v>0.1763821233623858</v>
       </c>
       <c r="J2" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K2" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07709307483307482</v>
+        <v>0.07622648002518584</v>
       </c>
       <c r="M2" t="n">
-        <v>3.799949499974066</v>
+        <v>3.796651551188597</v>
       </c>
       <c r="N2" t="n">
-        <v>21.09844333439019</v>
+        <v>21.05899337687198</v>
       </c>
       <c r="O2" t="n">
-        <v>4.593304184831458</v>
+        <v>4.589007885902135</v>
       </c>
       <c r="P2" t="n">
-        <v>338.9551651515908</v>
+        <v>338.9722193492363</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11615,28 +11646,28 @@
         <v>0.1106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1626953886694804</v>
+        <v>0.1601452088271473</v>
       </c>
       <c r="J3" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K3" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05845043507815473</v>
+        <v>0.05695525219802211</v>
       </c>
       <c r="M3" t="n">
-        <v>3.956777543747812</v>
+        <v>3.959248898910931</v>
       </c>
       <c r="N3" t="n">
-        <v>23.73110295706368</v>
+        <v>23.71893871790641</v>
       </c>
       <c r="O3" t="n">
-        <v>4.871457990895917</v>
+        <v>4.870209309455438</v>
       </c>
       <c r="P3" t="n">
-        <v>317.1711272621526</v>
+        <v>317.1988666056961</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11693,28 +11724,28 @@
         <v>0.0882</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0643051880535237</v>
+        <v>0.06363110084828436</v>
       </c>
       <c r="J4" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K4" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01074261646082697</v>
+        <v>0.010586480907537</v>
       </c>
       <c r="M4" t="n">
-        <v>3.754309768150532</v>
+        <v>3.747118285417998</v>
       </c>
       <c r="N4" t="n">
-        <v>21.19352772072725</v>
+        <v>21.13654149452943</v>
       </c>
       <c r="O4" t="n">
-        <v>4.603642875020525</v>
+        <v>4.597449455353416</v>
       </c>
       <c r="P4" t="n">
-        <v>322.3160526691666</v>
+        <v>322.3233849899128</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11752,7 +11783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E348"/>
+  <dimension ref="A1:E349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21151,6 +21182,33 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-35.462939646908175,174.4359693975266</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-35.46343349519481,174.43668646319745</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-35.46368204567063,174.4375330328829</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
